--- a/estandar-d/templates/4-1-reporte-rendimiento-tecnico.xlsx
+++ b/estandar-d/templates/4-1-reporte-rendimiento-tecnico.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Reporte de rendimiento técnico de la solución de transformación digital, elaborado Manual de Transformación Digital con IA · Producto del Elemento 4 · Optimizar · Excel</t>
+          <t>Reporte de rendimiento técnico de la solución de modernización digital, elaborado Manual de Modernización Digital con IA · Producto del Elemento 4 · Optimizar · Excel</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">

--- a/estandar-d/templates/4-1-reporte-rendimiento-tecnico.xlsx
+++ b/estandar-d/templates/4-1-reporte-rendimiento-tecnico.xlsx
@@ -14,7 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 2 · Comparativo indicadore" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 3 · Rendimiento de compone" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tabla 1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Referencia de trabajo del F21'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tu turno · preguntas guía'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Hoja 1 · Métricas de rendimient'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Hoja 2 · Comparativo indicadore'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Hoja 3 · Rendimiento de compone'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -31,17 +38,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <color rgb="004B5563"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,8 +61,13 @@
         <fgColor rgb="0028467E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,16 +75,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3E4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3E4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3E4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3E4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +477,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mi CompañIA</t>
@@ -484,7 +514,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MiPyME</t>
@@ -531,7 +561,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -562,17 +592,17 @@
       <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Comparativo contra umbrales de la propuesta Por cada métrica: ¿cuál era el umbral definido en la propuesta? ¿Cuál fue el resultado real? ¿Se cumplió (S/N)?</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -588,17 +618,17 @@
       <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Identificación del reporte Periodo exacto de medición (fecha inicio y fecha fin), herramientas utilizadas para cada métrica y nombre del responsable de elaborar el reporte.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -624,7 +654,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha/Periodo</t>
@@ -677,14 +707,14 @@
       <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
@@ -697,14 +727,14 @@
       <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr"/>
@@ -717,14 +747,14 @@
       <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
@@ -737,14 +767,14 @@
       <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
@@ -757,14 +787,14 @@
       <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -787,7 +817,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Indicador técnico</t>
@@ -829,18 +859,18 @@
       <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Latencia promedio (ms)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2">
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3">
         <f>%</f>
         <v/>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -857,18 +887,18 @@
       <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>CPU promedio (%)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2">
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3">
         <f>%</f>
         <v/>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -907,7 +937,7 @@
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Componente de IA</t>
@@ -954,13 +984,13 @@
       <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
@@ -972,13 +1002,13 @@
       <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr"/>

--- a/estandar-d/templates/4-1-reporte-rendimiento-tecnico.xlsx
+++ b/estandar-d/templates/4-1-reporte-rendimiento-tecnico.xlsx
@@ -7,16 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referencia de trabajo del F21" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos del documento" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tu turno · preguntas guía" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 1 · Métricas de rendimient" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 2 · Comparativo indicadore" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 3 · Rendimiento de compone" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tabla 1'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Referencia de trabajo del F21'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Datos del documento'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tu turno · preguntas guía'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Hoja 1 · Métricas de rendimient'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Hoja 2 · Comparativo indicadore'!$1:$1</definedName>
@@ -29,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +40,24 @@
       <name val="Calibri"/>
       <color rgb="004B5563"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00529ED7"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0028467E"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0028467E"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -93,9 +110,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -469,28 +498,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mi CompañIA</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Reporte de rendimiento técnico de la solución de modernización digital, elaborado Manual de Modernización Digital con IA · Producto del Elemento 4 · Optimizar · Excel</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Producto 4.1 Hoja editable · Excel Mi CompañIA · FUNDES</t>
+          <t>PLANTILLA DE TRABAJO · ESTÁNDAR D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Reporte de rendimiento técnico de la solución de modernización digital, elaborado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sobre este template. Producto de medición técnica de la solución en operación real. Registra las métricas de rendimiento (disponibilidad, latencia, tasa de error, consumo de recursos), las compara contra los umbrales definidos en la propuesta, analiza el rendimiento de los componentes de IA (calidad de respuestas, tiempos, costos por consulta) e identifica el responsable, las herramientas de medición y el periodo de análisis. Excel es el formato natural para este producto: permite añadir filas de medición y calcular promedios automáticamente. Excel es el formato natural para este producto: permite añadir filas de medición, calcular promedios y comparativos automáticamente. Llénalo con datos reales de TU proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de trabajo del F21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>•  (a) Contiene las métricas de rendimiento de la solución de modernización recolectadas: disponibilidad, latencia, tasa de error y consumo de recursos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>•  (b) Incluye la comparación de los indicadores técnicos contra los umbrales definidos en los requerimientos de la propuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>•  (c) Tiene el análisis de rendimiento de los componentes de IA: calidad de respuestas, ejemplos representativos, tiempos de procesamiento y costos por consulta</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>•  (d) Proporciona información sobre el periodo de medición, las herramientas utilizadas y el nombre del responsable del reporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Caso pedagógico Distribuidora El Surtido (ilustrativo): El Surtido — Periodo: 1-30 junio 2025 · Responsable: Consultoría Digital MX. Herramientas: UptimeRobot (disponibilidad), Datadog APM (latencia/errores), OpenAI Dashboard (tokens). Disponibilidad: 99.7% (umbral propuesta: 99.5% — CUMPLIDO). Latencia promedio: 1.8s (umbral: &lt; 3s — CUMPLIDO). Tasa de error: 0.8% (umbral: &lt; 2% — CUMPLIDO). IA: 96.2% de pedidos interpretados correctamente (meta: 90% — SUPERADO). Tiempo de procesamiento IA: 1.2s promedio. Costo por consulta: $0.003 USD. Consumo total junio: $12.40 USD (presupuesto mensual: $20 USD — DENTRO DEL LÍMITE).</t>
         </is>
       </c>
     </row>
@@ -515,32 +588,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>MiPyME</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr"/>
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr"/>
+      <c r="D1" s="5" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Consultor</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Responsable MiPyME</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -562,73 +635,73 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Pregunta guía</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Tu respuesta (llena con datos de TU proyecto real)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Métricas de rendimiento del periodo Para el periodo de medición: Disponibilidad (% de uptime), Latencia promedio (ms o segundos), Tasa de error (%), Consumo de recursos del servidor (CPU%, RAM%). ¿Con qué herramienta mediste cada métrica?</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Comparativo contra umbrales de la propuesta Por cada métrica: ¿cuál era el umbral definido en la propuesta? ¿Cuál fue el resultado real? ¿Se cumplió (S/N)?</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Rendimiento de los componentes de IA ¿Cuál es el porcentaje de respuestas correctas del componente de IA? Incluye ejemplos representativos (un caso bueno, un caso con error). ¿Cuál es el tiempo promedio de respuesta de la IA? ¿Cuál es el costo promedio por consulta y el costo total del periodo?</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Identificación del reporte Periodo exacto de medición (fecha inicio y fecha fin), herramientas utilizadas para cada métrica y nombre del responsable de elaborar el reporte.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -655,146 +728,146 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Fecha/Periodo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Disponibilidad (%)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Latencia prom. (ms)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Tasa error (%)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>CPU (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>RAM (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Herramienta de medición</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Notas / Incidencias</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="A2" s="6" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="A3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="A4" s="6" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="A6" s="6" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="A8" s="6" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr"/>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -813,106 +886,106 @@
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Indicador técnico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Umbral de la propuesta</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Resultado real del periodo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Variación %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Cumplido (S/N)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Disponibilidad (%)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2">
-        <f>%</f>
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
+      <c r="D2" s="6">
+        <f>IFERROR(ROUND((C2-B2)/B2*100,2),"")</f>
         <v/>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Latencia promedio (ms)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3">
-        <f>%</f>
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7">
+        <f>IFERROR(ROUND((C3-B3)/B3*100,2),"")</f>
         <v/>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Tasa de error (%)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2">
-        <f>%</f>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6">
+        <f>IFERROR(ROUND((C4-B4)/B4*100,2),"")</f>
         <v/>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>CPU promedio (%)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3">
-        <f>%</f>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7">
+        <f>IFERROR(ROUND((C5-B5)/B5*100,2),"")</f>
         <v/>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>RAM promedio (%)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2">
-        <f>%</f>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6">
+        <f>IFERROR(ROUND((C6-B6)/B6*100,2),"")</f>
         <v/>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -938,86 +1011,86 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Componente de IA</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>% respuestas correctas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Ejemplo de respuesta correcta</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Ejemplo de respuesta incorrecta</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Tiempo prom. (ms)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Costo/consulta (USD)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Costo total periodo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="A2" s="6" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="A3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="A4" s="6" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="A6" s="6" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
